--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,6 +643,30 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>archery_range</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>양궁 사거리</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/ArcheryRangeMap.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,7 +644,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
         <v>6</v>
       </c>
@@ -662,6 +661,29 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/ArcheryRangeMap.unity</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>archery_shootoff</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>한 발 승부</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Assets/Art/Scenes/ArcheryRangeMap.unity</t>
         </is>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,6 +689,29 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DodgeMap</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>피하기 경기장</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/DodgeMap.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,29 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SkydivePyramid</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>하늘 피라미드</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/SkydivePyramidMap.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,6 +735,29 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SkydiveChimney</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>굴뚝 시제품</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/SkydiveChimneyMap.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,6 +758,29 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SkydiveSpiral</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>피라미드 개정안</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/SkydiveSpiralMap.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,29 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SkydiveCylinder</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>원통 시제품</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/SkydiveCylinderMap.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,65 +599,65 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SkydiveMap</t>
+          <t>archery_circle</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>스카이다이브 맵</t>
+          <t>원형 사대</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Assets/Art/Scenes/SkydiveMap.unity</t>
+          <t>Assets/Art/Scenes/ArcheryCircleMap.unity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>archery_circle</t>
+          <t>archery_range</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>원형 사대</t>
+          <t>양궁 사거리</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Assets/Art/Scenes/ArcheryCircleMap.unity</t>
+          <t>Assets/Art/Scenes/ArcheryRangeMap.unity</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>archery_range</t>
+          <t>archery_shootoff</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>양궁 사거리</t>
+          <t>한 발 승부</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -668,137 +668,45 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>archery_shootoff</t>
+          <t>DodgeMap</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>한 발 승부</t>
+          <t>피하기 경기장</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Assets/Art/Scenes/ArcheryRangeMap.unity</t>
+          <t>Assets/Art/Scenes/DodgeMap.unity</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" t="n">
         <v>8</v>
       </c>
-      <c r="C12" t="n">
-        <v>9</v>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DodgeMap</t>
+          <t>SkydiveCylinder</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>피하기 경기장</t>
+          <t>원통 시제품</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>Assets/Art/Scenes/DodgeMap.unity</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SkydivePyramid</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>하늘 피라미드</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Assets/Art/Scenes/SkydivePyramidMap.unity</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SkydiveChimney</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>굴뚝 시제품</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Assets/Art/Scenes/SkydiveChimneyMap.unity</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SkydiveSpiral</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>피라미드 개정안</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Assets/Art/Scenes/SkydiveSpiralMap.unity</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SkydiveCylinder</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>원통 시제품</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>Assets/Art/Scenes/SkydiveCylinderMap.unity</t>
         </is>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,114 +599,68 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>archery_circle</t>
+          <t>archery_shootoff</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>원형 사대</t>
+          <t>한 발 승부</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Assets/Art/Scenes/ArcheryCircleMap.unity</t>
+          <t>Assets/Art/Scenes/ArcheryRangeMap.unity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>archery_range</t>
+          <t>DodgeMap</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>양궁 사거리</t>
+          <t>피하기 경기장</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Assets/Art/Scenes/ArcheryRangeMap.unity</t>
+          <t>Assets/Art/Scenes/DodgeMap.unity</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>archery_shootoff</t>
+          <t>SkydiveCylinder</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>한 발 승부</t>
+          <t>원통 시제품</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>Assets/Art/Scenes/ArcheryRangeMap.unity</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C11" t="n">
-        <v>9</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DodgeMap</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>피하기 경기장</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Assets/Art/Scenes/DodgeMap.unity</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="n">
-        <v>12</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SkydiveCylinder</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>원통 시제품</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
         <is>
           <t>Assets/Art/Scenes/SkydiveCylinderMap.unity</t>
         </is>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,6 +666,29 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>archery_catapult</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>투석기 사냥</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/ArcheryRangeMap.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,6 +689,29 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MountedArcheryMap</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>들판</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/MountedArcheryMap.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,29 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KnockbackArena</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>허공 원판</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/KnockbackMap.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
